--- a/scripts/output/default-profile-snapshot.xlsx
+++ b/scripts/output/default-profile-snapshot.xlsx
@@ -1703,14 +1703,14 @@
         <v>8</v>
       </c>
       <c r="C11" s="1">
-        <v>0.03</v>
+        <v>0.004</v>
       </c>
       <c r="D11" s="1">
         <v>0.005</v>
       </c>
       <c r="E11" s="10">
         <f>IF(D11&gt;0,(C11-F11)/D11,0)</f>
-        <v>5.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1">
         <v>0.004</v>
